--- a/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-30T11:02:30+00:00</t>
+    <t>2023-11-06T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person-role</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person-role</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:17:56+00:00</t>
+    <t>2023-11-07T10:08:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:08:49+00:00</t>
+    <t>2023-11-07T10:16:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:16:09+00:00</t>
+    <t>2023-11-07T10:18:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:18:25+00:00</t>
+    <t>2023-11-07T10:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:25:25+00:00</t>
+    <t>2023-11-07T10:39:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:39:28+00:00</t>
+    <t>2023-11-07T10:47:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-related-person-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:47:16+00:00</t>
+    <t>2023-11-07T10:49:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
